--- a/services/data_raw/eurostat/AT_cars_road_eqr_carpda.xlsx
+++ b/services/data_raw/eurostat/AT_cars_road_eqr_carpda.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,89 +417,89 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>freq</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>mot_nrg</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>geo\TIME_PERIOD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -572,7 +560,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -587,7 +575,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Petroleum products [PET]</t>
+          <t>Petrol [PET]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -633,7 +621,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,7 +680,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -753,7 +741,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -814,7 +802,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -875,7 +863,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -936,7 +924,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -997,7 +985,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1058,7 +1046,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1119,7 +1107,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1180,7 +1168,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1241,7 +1229,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1302,7 +1290,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1363,7 +1351,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1412,7 +1400,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1461,7 +1449,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1522,7 +1510,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">

--- a/services/data_raw/eurostat/AT_cars_road_eqr_carpda.xlsx
+++ b/services/data_raw/eurostat/AT_cars_road_eqr_carpda.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,11 @@
           <t>2024</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -557,6 +562,9 @@
       </c>
       <c r="Q2" t="n">
         <v>253789</v>
+      </c>
+      <c r="R2" t="n">
+        <v>284978</v>
       </c>
     </row>
     <row r="3">
@@ -619,6 +627,9 @@
       <c r="Q3" t="n">
         <v>150676</v>
       </c>
+      <c r="R3" t="n">
+        <v>176600</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -636,7 +647,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Liquefied petroleum gases (LPG) [LPG]</t>
+          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,38 +656,43 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>134276</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>126503</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>122832</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>131756</v>
+      </c>
+      <c r="J4" t="n">
+        <v>163701</v>
+      </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>184150</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>176706</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>107771</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>91478</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>78567</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>77354</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>84004</v>
+      </c>
+      <c r="R4" t="n">
+        <v>79457</v>
       </c>
     </row>
     <row r="5">
@@ -695,7 +711,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Diesel [DIE]</t>
+          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -704,40 +720,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>181061</v>
+        <v>2259</v>
       </c>
       <c r="G5" t="n">
-        <v>172574</v>
+        <v>1836</v>
       </c>
       <c r="H5" t="n">
-        <v>180510</v>
+        <v>1893</v>
       </c>
       <c r="I5" t="n">
-        <v>189139</v>
+        <v>3305</v>
       </c>
       <c r="J5" t="n">
-        <v>175590</v>
+        <v>6529</v>
       </c>
       <c r="K5" t="n">
-        <v>141159</v>
+        <v>6135</v>
       </c>
       <c r="L5" t="n">
-        <v>130468</v>
+        <v>10237</v>
       </c>
       <c r="M5" t="n">
-        <v>99196</v>
+        <v>18178</v>
       </c>
       <c r="N5" t="n">
-        <v>71808</v>
+        <v>29451</v>
       </c>
       <c r="O5" t="n">
-        <v>61537</v>
+        <v>28238</v>
       </c>
       <c r="P5" t="n">
-        <v>61187</v>
+        <v>36705</v>
       </c>
       <c r="Q5" t="n">
-        <v>58478</v>
+        <v>51611</v>
+      </c>
+      <c r="R5" t="n">
+        <v>70207</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +775,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Natural gas [GAS]</t>
+          <t>Plug-in hybrid petrol-electric [ELC_PET_PI]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -765,40 +784,43 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>455</v>
+        <v>154</v>
       </c>
       <c r="G6" t="n">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="H6" t="n">
-        <v>167</v>
+        <v>931</v>
       </c>
       <c r="I6" t="n">
-        <v>119</v>
+        <v>1087</v>
       </c>
       <c r="J6" t="n">
-        <v>114</v>
+        <v>1632</v>
       </c>
       <c r="K6" t="n">
-        <v>110</v>
+        <v>2218</v>
       </c>
       <c r="L6" t="n">
-        <v>421</v>
+        <v>2111</v>
       </c>
       <c r="M6" t="n">
-        <v>386</v>
+        <v>7202</v>
       </c>
       <c r="N6" t="n">
-        <v>70</v>
+        <v>13600</v>
       </c>
       <c r="O6" t="n">
-        <v>51</v>
+        <v>12466</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>16262</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>15061</v>
+      </c>
+      <c r="R6" t="n">
+        <v>26936</v>
       </c>
     </row>
     <row r="7">
@@ -817,7 +839,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Electricity [ELC]</t>
+          <t>Diesel [DIE]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -826,40 +848,43 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>654</v>
+        <v>181061</v>
       </c>
       <c r="G7" t="n">
-        <v>1281</v>
+        <v>172574</v>
       </c>
       <c r="H7" t="n">
-        <v>1677</v>
+        <v>180510</v>
       </c>
       <c r="I7" t="n">
-        <v>3826</v>
+        <v>189139</v>
       </c>
       <c r="J7" t="n">
-        <v>5433</v>
+        <v>175590</v>
       </c>
       <c r="K7" t="n">
-        <v>6757</v>
+        <v>141159</v>
       </c>
       <c r="L7" t="n">
-        <v>9242</v>
+        <v>130468</v>
       </c>
       <c r="M7" t="n">
-        <v>15972</v>
+        <v>99196</v>
       </c>
       <c r="N7" t="n">
-        <v>33366</v>
+        <v>71808</v>
       </c>
       <c r="O7" t="n">
-        <v>34165</v>
+        <v>61537</v>
       </c>
       <c r="P7" t="n">
-        <v>47621</v>
+        <v>61187</v>
       </c>
       <c r="Q7" t="n">
-        <v>44622</v>
+        <v>58478</v>
+      </c>
+      <c r="R7" t="n">
+        <v>47725</v>
       </c>
     </row>
     <row r="8">
@@ -878,7 +903,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alternative energy [ALT]</t>
+          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -887,40 +912,43 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1285</v>
+        <v>180901</v>
       </c>
       <c r="G8" t="n">
-        <v>2074</v>
+        <v>172381</v>
       </c>
       <c r="H8" t="n">
-        <v>2389</v>
+        <v>179822</v>
       </c>
       <c r="I8" t="n">
-        <v>4317</v>
+        <v>188820</v>
       </c>
       <c r="J8" t="n">
-        <v>5868</v>
+        <v>175458</v>
       </c>
       <c r="K8" t="n">
-        <v>7406</v>
+        <v>140111</v>
       </c>
       <c r="L8" t="n">
-        <v>9841</v>
+        <v>126311</v>
       </c>
       <c r="M8" t="n">
-        <v>16393</v>
+        <v>90909</v>
       </c>
       <c r="N8" t="n">
-        <v>33466</v>
+        <v>58263</v>
       </c>
       <c r="O8" t="n">
-        <v>34242</v>
+        <v>48115</v>
       </c>
       <c r="P8" t="n">
-        <v>47642</v>
+        <v>46568</v>
       </c>
       <c r="Q8" t="n">
-        <v>44635</v>
+        <v>44132</v>
+      </c>
+      <c r="R8" t="n">
+        <v>33004</v>
       </c>
     </row>
     <row r="9">
@@ -939,7 +967,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
+          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -948,40 +976,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>134276</v>
+        <v>130</v>
       </c>
       <c r="G9" t="n">
-        <v>126503</v>
+        <v>90</v>
       </c>
       <c r="H9" t="n">
-        <v>122832</v>
+        <v>518</v>
       </c>
       <c r="I9" t="n">
-        <v>131756</v>
+        <v>169</v>
       </c>
       <c r="J9" t="n">
-        <v>163701</v>
+        <v>43</v>
       </c>
       <c r="K9" t="n">
-        <v>184150</v>
+        <v>1008</v>
       </c>
       <c r="L9" t="n">
-        <v>176706</v>
+        <v>4112</v>
       </c>
       <c r="M9" t="n">
-        <v>107771</v>
+        <v>7848</v>
       </c>
       <c r="N9" t="n">
-        <v>91478</v>
+        <v>12519</v>
       </c>
       <c r="O9" t="n">
-        <v>78567</v>
+        <v>12620</v>
       </c>
       <c r="P9" t="n">
-        <v>77354</v>
+        <v>13925</v>
       </c>
       <c r="Q9" t="n">
-        <v>84004</v>
+        <v>12479</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12837</v>
       </c>
     </row>
     <row r="10">
@@ -1000,7 +1031,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
+          <t>Plug-in hybrid diesel-electric [ELC_DIE_PI]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1009,40 +1040,43 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2259</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>1836</v>
+        <v>103</v>
       </c>
       <c r="H10" t="n">
-        <v>1893</v>
+        <v>170</v>
       </c>
       <c r="I10" t="n">
-        <v>3305</v>
+        <v>150</v>
       </c>
       <c r="J10" t="n">
-        <v>6529</v>
+        <v>89</v>
       </c>
       <c r="K10" t="n">
-        <v>6135</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>10237</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>18178</v>
+        <v>439</v>
       </c>
       <c r="N10" t="n">
-        <v>29451</v>
+        <v>1026</v>
       </c>
       <c r="O10" t="n">
-        <v>28238</v>
+        <v>802</v>
       </c>
       <c r="P10" t="n">
-        <v>36705</v>
+        <v>694</v>
       </c>
       <c r="Q10" t="n">
-        <v>51611</v>
+        <v>1867</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1884</v>
       </c>
     </row>
     <row r="11">
@@ -1061,7 +1095,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Plug-in hybrid petrol-electric [ELC_PET_PI]</t>
+          <t>Alternative energy [ALT]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1070,40 +1104,43 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>154</v>
+        <v>1285</v>
       </c>
       <c r="G11" t="n">
-        <v>331</v>
+        <v>2074</v>
       </c>
       <c r="H11" t="n">
-        <v>931</v>
+        <v>2389</v>
       </c>
       <c r="I11" t="n">
-        <v>1087</v>
+        <v>4317</v>
       </c>
       <c r="J11" t="n">
-        <v>1632</v>
+        <v>5868</v>
       </c>
       <c r="K11" t="n">
-        <v>2218</v>
+        <v>7406</v>
       </c>
       <c r="L11" t="n">
-        <v>2111</v>
+        <v>9841</v>
       </c>
       <c r="M11" t="n">
-        <v>7202</v>
+        <v>16393</v>
       </c>
       <c r="N11" t="n">
-        <v>13600</v>
+        <v>33466</v>
       </c>
       <c r="O11" t="n">
-        <v>12466</v>
+        <v>34242</v>
       </c>
       <c r="P11" t="n">
-        <v>16262</v>
+        <v>47642</v>
       </c>
       <c r="Q11" t="n">
-        <v>15061</v>
+        <v>44635</v>
+      </c>
+      <c r="R11" t="n">
+        <v>60653</v>
       </c>
     </row>
     <row r="12">
@@ -1122,7 +1159,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
+          <t>Electricity [ELC]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1131,40 +1168,43 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>180901</v>
+        <v>654</v>
       </c>
       <c r="G12" t="n">
-        <v>172381</v>
+        <v>1281</v>
       </c>
       <c r="H12" t="n">
-        <v>179822</v>
+        <v>1677</v>
       </c>
       <c r="I12" t="n">
-        <v>188820</v>
+        <v>3826</v>
       </c>
       <c r="J12" t="n">
-        <v>175458</v>
+        <v>5433</v>
       </c>
       <c r="K12" t="n">
-        <v>140111</v>
+        <v>6757</v>
       </c>
       <c r="L12" t="n">
-        <v>126311</v>
+        <v>9242</v>
       </c>
       <c r="M12" t="n">
-        <v>90909</v>
+        <v>15972</v>
       </c>
       <c r="N12" t="n">
-        <v>58263</v>
+        <v>33366</v>
       </c>
       <c r="O12" t="n">
-        <v>48115</v>
+        <v>34165</v>
       </c>
       <c r="P12" t="n">
-        <v>46568</v>
+        <v>47621</v>
       </c>
       <c r="Q12" t="n">
-        <v>44132</v>
+        <v>44622</v>
+      </c>
+      <c r="R12" t="n">
+        <v>60651</v>
       </c>
     </row>
     <row r="13">
@@ -1183,7 +1223,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
+          <t>Hydrogen and fuel cells [HYD_FCELL]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1192,40 +1232,43 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>518</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>169</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1008</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>4112</v>
+        <v>19</v>
       </c>
       <c r="M13" t="n">
-        <v>7848</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>12519</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>12620</v>
+        <v>14</v>
       </c>
       <c r="P13" t="n">
-        <v>13925</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>12479</v>
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1244,7 +1287,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Plug-in hybrid diesel-electric [ELC_DIE_PI]</t>
+          <t>Other renewable fuels [REN_OTH]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1253,40 +1296,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1026</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>802</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>694</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1867</v>
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1305,7 +1351,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hydrogen and fuel cells [HYD_FCELL]</t>
+          <t>Natural gas [GAS]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1314,40 +1360,43 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>279</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="L15" t="n">
-        <v>19</v>
+        <v>421</v>
       </c>
       <c r="M15" t="n">
-        <v>14</v>
+        <v>386</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="O15" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1366,7 +1415,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bioethanol [BIOETH]</t>
+          <t>Liquefied petroleum gases (LPG) [LPG]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1374,12 +1423,22 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
@@ -1396,6 +1455,9 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1415,7 +1477,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Biodiesel [BIODIE]</t>
+          <t>Other [OTH]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1423,12 +1485,24 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -1447,127 +1521,8 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bi-fuel [BIFUEL]</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>176</v>
-      </c>
-      <c r="G18" t="n">
-        <v>511</v>
-      </c>
-      <c r="H18" t="n">
-        <v>536</v>
-      </c>
-      <c r="I18" t="n">
-        <v>367</v>
-      </c>
-      <c r="J18" t="n">
-        <v>321</v>
-      </c>
-      <c r="K18" t="n">
-        <v>532</v>
-      </c>
-      <c r="L18" t="n">
-        <v>159</v>
-      </c>
-      <c r="M18" t="n">
-        <v>21</v>
-      </c>
-      <c r="N18" t="n">
-        <v>16</v>
-      </c>
-      <c r="O18" t="n">
-        <v>12</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Other [OTH]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
+      <c r="R17" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
